--- a/Timesheet-Project/Timesheet 3/Kayden/Kayden_Padayachee_April_FinalWeek.xlsx
+++ b/Timesheet-Project/Timesheet 3/Kayden/Kayden_Padayachee_April_FinalWeek.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://advtechonline-my.sharepoint.com/personal/st10385543_vcconnect_edu_za/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_LwazisileMhlambi_2026\Timesheet-Project\Timesheet 3\Kayden\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{65193892-D3A1-4589-BA65-0C0416D3D673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{882E23A6-E25D-467D-A452-1BDC099F27F9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE22A852-02BD-4802-882D-C23E89EA1D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="252">
   <si>
     <t>Consultant</t>
   </si>
@@ -167,9 +167,6 @@
     <t>Continued with day one of the project,
 and I finished it before the end of the day. 
 I attended High Performers Retrospective meeting.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      3:22</t>
   </si>
   <si>
     <t>Attended Daily Standup.
@@ -861,7 +858,7 @@
     <numFmt numFmtId="166" formatCode="_ [$R-1C09]\ * #,##0.00_ ;_ [$R-1C09]\ * \-#,##0.00_ ;_ [$R-1C09]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="[$R-1C09]#,##0.00;\-[$R-1C09]#,##0.00"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1966,13 +1963,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1988,21 +2000,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2061,147 +2058,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="103">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2874,6 +2730,147 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{6758C6CA-2356-4535-9D9D-86230C423211}"/>
@@ -3282,26 +3279,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}" name="WorkType" displayName="WorkType" ref="H2:H76" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}" name="WorkType" displayName="WorkType" ref="H2:H76" totalsRowShown="0" headerRowDxfId="102" dataDxfId="101">
   <autoFilter ref="H2:H76" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H3:H76">
     <sortCondition ref="H64:H76"/>
   </sortState>
   <tableColumns count="1">
-    <tableColumn id="2" xr3:uid="{234A6588-4DEA-4067-9367-AEAFE02CA40D}" name="Resource" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{234A6588-4DEA-4067-9367-AEAFE02CA40D}" name="Resource" dataDxfId="100"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}" name="ProjectTable" displayName="ProjectTable" ref="F2:F40" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}" name="ProjectTable" displayName="ProjectTable" ref="F2:F40" totalsRowShown="0" headerRowDxfId="99" dataDxfId="98" tableBorderDxfId="97">
   <autoFilter ref="F2:F40" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F3:F19">
     <sortCondition ref="F2:F19"/>
   </sortState>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{D9788319-59C4-447A-9364-6F4EF6730453}" name="Description" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D9788319-59C4-447A-9364-6F4EF6730453}" name="Description" dataDxfId="96"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3578,18 +3575,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B63D3D5-6C83-45F2-B2A7-43EE15BF1EF3}">
   <dimension ref="A5:J72"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -3598,7 +3595,7 @@
       </c>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -3610,7 +3607,7 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="37"/>
       <c r="B7" s="46"/>
       <c r="C7" s="37"/>
@@ -3619,7 +3616,7 @@
       <c r="H7" s="40"/>
       <c r="J7" s="41"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -3651,7 +3648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="63">
+    <row r="9" spans="1:10" ht="63" x14ac:dyDescent="0.2">
       <c r="A9" s="22">
         <v>46113</v>
       </c>
@@ -3682,7 +3679,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="37.5">
+    <row r="10" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>46113</v>
       </c>
@@ -3712,7 +3709,7 @@
         <v>0.74583333333333335</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="75.75">
+    <row r="11" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46114</v>
       </c>
@@ -3733,7 +3730,7 @@
         <v>20</v>
       </c>
       <c r="H11" s="29">
-        <f t="shared" ref="H11:H12" si="0">J11-I11</f>
+        <f t="shared" ref="H11" si="0">J11-I11</f>
         <v>0.20208333333333334</v>
       </c>
       <c r="I11" s="30">
@@ -3743,7 +3740,7 @@
         <v>0.53541666666666665</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="37.5">
+    <row r="12" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>46114</v>
       </c>
@@ -3773,7 +3770,7 @@
         <v>0.71736111111111112</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="47">
         <v>46115</v>
       </c>
@@ -3802,7 +3799,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="31">
         <v>46116</v>
       </c>
@@ -3821,7 +3818,7 @@
       <c r="I14" s="35"/>
       <c r="J14" s="35"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="31">
         <v>46117</v>
       </c>
@@ -3840,7 +3837,7 @@
       <c r="I15" s="35"/>
       <c r="J15" s="35"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="47">
         <v>46118</v>
       </c>
@@ -3871,7 +3868,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="50.25">
+    <row r="17" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
       <c r="A17" s="22">
         <v>46119</v>
       </c>
@@ -3902,7 +3899,7 @@
         <v>0.53194444444444444</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="37.5">
+    <row r="18" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A18" s="22">
         <v>46119</v>
       </c>
@@ -3932,7 +3929,7 @@
         <v>0.73958333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="50.25">
+    <row r="19" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
       <c r="A19" s="22">
         <v>46120</v>
       </c>
@@ -3963,7 +3960,7 @@
         <v>0.53402777777777777</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="37.5">
+    <row r="20" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A20" s="22">
         <v>46119</v>
       </c>
@@ -3993,7 +3990,7 @@
         <v>0.7270833333333333</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="50.25">
+    <row r="21" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
       <c r="A21" s="22">
         <v>46121</v>
       </c>
@@ -4024,7 +4021,7 @@
         <v>0.52500000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="37.5">
+    <row r="22" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A22" s="22">
         <v>46121</v>
       </c>
@@ -4054,7 +4051,7 @@
         <v>0.72569444444444442</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="50.25">
+    <row r="23" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
       <c r="A23" s="22">
         <v>46122</v>
       </c>
@@ -4085,7 +4082,7 @@
         <v>0.53194444444444444</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="37.5">
+    <row r="24" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A24" s="22">
         <v>46122</v>
       </c>
@@ -4115,7 +4112,7 @@
         <v>0.73611111111111116</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="31">
         <v>46123</v>
       </c>
@@ -4134,7 +4131,7 @@
       <c r="I25" s="35"/>
       <c r="J25" s="35"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="31">
         <v>46124</v>
       </c>
@@ -4153,7 +4150,7 @@
       <c r="I26" s="35"/>
       <c r="J26" s="35"/>
     </row>
-    <row r="27" spans="1:10" ht="75.75">
+    <row r="27" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
       <c r="A27" s="22">
         <v>46125</v>
       </c>
@@ -4184,7 +4181,7 @@
         <v>0.53541666666666665</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="63">
+    <row r="28" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
       <c r="A28" s="22">
         <v>46125</v>
       </c>
@@ -4204,8 +4201,9 @@
       <c r="G28" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="H28" s="29" t="s">
-        <v>34</v>
+      <c r="H28" s="29">
+        <f t="shared" si="1"/>
+        <v>0.14027777777777783</v>
       </c>
       <c r="I28" s="30">
         <v>0.57430555555555551</v>
@@ -4214,7 +4212,7 @@
         <v>0.71458333333333335</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="88.5">
+    <row r="29" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
       <c r="A29" s="22">
         <v>46126</v>
       </c>
@@ -4232,7 +4230,7 @@
         <v>16</v>
       </c>
       <c r="G29" s="28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H29" s="29">
         <f t="shared" si="1"/>
@@ -4245,7 +4243,7 @@
         <v>0.54305555555555551</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="63">
+    <row r="30" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
         <v>46126</v>
       </c>
@@ -4257,13 +4255,13 @@
       </c>
       <c r="D30" s="27"/>
       <c r="E30" s="27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F30" s="27" t="s">
         <v>16</v>
       </c>
       <c r="G30" s="28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H30" s="29">
         <f t="shared" si="1"/>
@@ -4276,7 +4274,7 @@
         <v>0.73472222222222228</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="63">
+    <row r="31" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
       <c r="A31" s="22">
         <v>46127</v>
       </c>
@@ -4294,7 +4292,7 @@
         <v>16</v>
       </c>
       <c r="G31" s="28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H31" s="29">
         <f t="shared" si="1"/>
@@ -4307,7 +4305,7 @@
         <v>0.53194444444444444</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="63">
+    <row r="32" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
       <c r="A32" s="22">
         <v>46127</v>
       </c>
@@ -4325,7 +4323,7 @@
         <v>16</v>
       </c>
       <c r="G32" s="28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H32" s="29">
         <f t="shared" si="1"/>
@@ -4338,7 +4336,7 @@
         <v>0.72916666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="63">
+    <row r="33" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>46128</v>
       </c>
@@ -4356,7 +4354,7 @@
         <v>16</v>
       </c>
       <c r="G33" s="28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H33" s="29">
         <f t="shared" si="1"/>
@@ -4369,7 +4367,7 @@
         <v>0.53263888888888888</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="63">
+    <row r="34" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
       <c r="A34" s="22">
         <v>46128</v>
       </c>
@@ -4387,7 +4385,7 @@
         <v>16</v>
       </c>
       <c r="G34" s="28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H34" s="29">
         <f t="shared" si="1"/>
@@ -4400,7 +4398,7 @@
         <v>0.73958333333333337</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="75.75">
+    <row r="35" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>46129</v>
       </c>
@@ -4418,7 +4416,7 @@
         <v>16</v>
       </c>
       <c r="G35" s="28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H35" s="29">
         <f t="shared" si="1"/>
@@ -4431,7 +4429,7 @@
         <v>0.54027777777777775</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="63">
+    <row r="36" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>46129</v>
       </c>
@@ -4449,7 +4447,7 @@
         <v>16</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H36" s="29">
         <f t="shared" si="1"/>
@@ -4462,7 +4460,7 @@
         <v>0.7270833333333333</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="12.75">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="31">
         <v>46130</v>
       </c>
@@ -4481,7 +4479,7 @@
       <c r="I37" s="35"/>
       <c r="J37" s="35"/>
     </row>
-    <row r="38" spans="1:10" ht="12.75">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="31">
         <v>46131</v>
       </c>
@@ -4500,7 +4498,7 @@
       <c r="I38" s="35"/>
       <c r="J38" s="35"/>
     </row>
-    <row r="39" spans="1:10" ht="50.25">
+    <row r="39" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
       <c r="A39" s="22">
         <v>46132</v>
       </c>
@@ -4518,7 +4516,7 @@
         <v>16</v>
       </c>
       <c r="G39" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H39" s="29">
         <f t="shared" si="1"/>
@@ -4531,7 +4529,7 @@
         <v>0.53541666666666665</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="37.5">
+    <row r="40" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A40" s="22">
         <v>46132</v>
       </c>
@@ -4549,7 +4547,7 @@
         <v>16</v>
       </c>
       <c r="G40" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H40" s="29">
         <v>0.1451388888888889</v>
@@ -4561,7 +4559,7 @@
         <v>0.72013888888888888</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="37.5">
+    <row r="41" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
       <c r="A41" s="22">
         <v>46133</v>
       </c>
@@ -4579,7 +4577,7 @@
         <v>16</v>
       </c>
       <c r="G41" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H41" s="29">
         <f t="shared" si="1"/>
@@ -4592,7 +4590,7 @@
         <v>0.53888888888888886</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="37.5">
+    <row r="42" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A42" s="22">
         <v>46133</v>
       </c>
@@ -4610,7 +4608,7 @@
         <v>16</v>
       </c>
       <c r="G42" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H42" s="29">
         <f t="shared" si="1"/>
@@ -4623,7 +4621,7 @@
         <v>0.71180555555555558</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="37.5">
+    <row r="43" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
       <c r="A43" s="22">
         <v>46134</v>
       </c>
@@ -4641,7 +4639,7 @@
         <v>16</v>
       </c>
       <c r="G43" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H43" s="29">
         <f t="shared" si="1"/>
@@ -4654,7 +4652,7 @@
         <v>0.5395833333333333</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="37.5">
+    <row r="44" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A44" s="22">
         <v>46134</v>
       </c>
@@ -4672,7 +4670,7 @@
         <v>16</v>
       </c>
       <c r="G44" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H44" s="29">
         <f t="shared" si="1"/>
@@ -4685,7 +4683,7 @@
         <v>0.72430555555555554</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="37.5">
+    <row r="45" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
       <c r="A45" s="22">
         <v>46135</v>
       </c>
@@ -4703,7 +4701,7 @@
         <v>16</v>
       </c>
       <c r="G45" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H45" s="29">
         <f t="shared" si="1"/>
@@ -4716,7 +4714,7 @@
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="37.5">
+    <row r="46" spans="1:10" ht="37.799999999999997" x14ac:dyDescent="0.2">
       <c r="A46" s="22">
         <v>46135</v>
       </c>
@@ -4730,9 +4728,11 @@
       <c r="E46" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="F46" s="27"/>
+      <c r="F46" s="27" t="s">
+        <v>16</v>
+      </c>
       <c r="G46" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H46" s="29">
         <f t="shared" si="1"/>
@@ -4745,7 +4745,7 @@
         <v>0.7104166666666667</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="37.5">
+    <row r="47" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
       <c r="A47" s="22">
         <v>46136</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>16</v>
       </c>
       <c r="G47" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H47" s="29">
         <f t="shared" si="1"/>
@@ -4776,7 +4776,7 @@
         <v>0.53402777777777777</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="12.75">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="22">
         <v>46136</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>16</v>
       </c>
       <c r="G48" s="28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H48" s="29">
         <f t="shared" si="1"/>
@@ -4807,17 +4807,25 @@
         <v>0.60347222222222219</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="25.5">
-      <c r="A49" s="22"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="27"/>
+    <row r="49" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
+      <c r="A49" s="22">
+        <v>46136</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>14</v>
+      </c>
       <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
+      <c r="E49" s="27" t="s">
+        <v>35</v>
+      </c>
       <c r="F49" s="27" t="s">
         <v>16</v>
       </c>
       <c r="G49" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H49" s="29">
         <f t="shared" si="1"/>
@@ -4830,7 +4838,7 @@
         <v>0.61527777777777781</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="63">
+    <row r="50" spans="1:10" ht="63" x14ac:dyDescent="0.2">
       <c r="A50" s="22">
         <v>46136</v>
       </c>
@@ -4848,7 +4856,7 @@
         <v>16</v>
       </c>
       <c r="G50" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H50" s="29">
         <f t="shared" si="1"/>
@@ -4861,7 +4869,7 @@
         <v>0.71597222222222223</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="12.75">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="31">
         <v>46137</v>
       </c>
@@ -4880,7 +4888,7 @@
       <c r="I51" s="35"/>
       <c r="J51" s="35"/>
     </row>
-    <row r="52" spans="1:10" ht="12.75">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="31">
         <v>46138</v>
       </c>
@@ -4899,7 +4907,7 @@
       <c r="I52" s="35"/>
       <c r="J52" s="35"/>
     </row>
-    <row r="53" spans="1:10" ht="12.75">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="47">
         <v>46139</v>
       </c>
@@ -4917,7 +4925,7 @@
         <v>16</v>
       </c>
       <c r="G53" s="49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H53" s="50">
         <f t="shared" si="1"/>
@@ -4930,9 +4938,9 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="37.5">
+    <row r="54" spans="1:10" ht="50.4" x14ac:dyDescent="0.2">
       <c r="A54" s="122" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B54" s="122" t="s">
         <v>28</v>
@@ -4948,7 +4956,7 @@
         <v>16</v>
       </c>
       <c r="G54" s="123" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H54" s="124">
         <v>0.2013888888888889</v>
@@ -4960,9 +4968,9 @@
         <v>0.53263888888888888</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="63">
+    <row r="55" spans="1:10" ht="63" x14ac:dyDescent="0.2">
       <c r="A55" s="122" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B55" s="122" t="s">
         <v>28</v>
@@ -4978,7 +4986,7 @@
         <v>16</v>
       </c>
       <c r="G55" s="123" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H55" s="124">
         <v>0.13402777777777777</v>
@@ -4990,9 +4998,9 @@
         <v>0.70972222222222225</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="50.25">
+    <row r="56" spans="1:10" ht="63" x14ac:dyDescent="0.2">
       <c r="A56" s="122" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B56" s="122" t="s">
         <v>13</v>
@@ -5008,7 +5016,7 @@
         <v>16</v>
       </c>
       <c r="G56" s="123" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H56" s="124">
         <v>0.16944444444444445</v>
@@ -5020,9 +5028,9 @@
         <v>0.53888888888888886</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="50.25">
+    <row r="57" spans="1:10" ht="63" x14ac:dyDescent="0.2">
       <c r="A57" s="122" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B57" s="122" t="s">
         <v>13</v>
@@ -5038,7 +5046,7 @@
         <v>16</v>
       </c>
       <c r="G57" s="123" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H57" s="124">
         <v>0.17222222222222222</v>
@@ -5050,9 +5058,9 @@
         <v>0.71319444444444446</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="13.9" customHeight="1">
+    <row r="58" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="122" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="122" t="s">
         <v>19</v>
@@ -5068,7 +5076,7 @@
         <v>16</v>
       </c>
       <c r="G58" s="123" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H58" s="124">
         <v>0.20347222222222222</v>
@@ -5080,9 +5088,9 @@
         <v>0.53888888888888886</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="13.9" customHeight="1">
+    <row r="59" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="122" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B59" s="122" t="s">
         <v>19</v>
@@ -5098,7 +5106,7 @@
         <v>16</v>
       </c>
       <c r="G59" s="123" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H59" s="124">
         <v>0.1423611111111111</v>
@@ -5110,7 +5118,7 @@
         <v>0.72013888888888888</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="13.9" customHeight="1">
+    <row r="60" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="126"/>
       <c r="B60" s="126"/>
       <c r="C60" s="126"/>
@@ -5122,7 +5130,7 @@
       <c r="I60" s="129"/>
       <c r="J60" s="129"/>
     </row>
-    <row r="61" spans="1:10" ht="13.9" customHeight="1">
+    <row r="61" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="126"/>
       <c r="B61" s="126"/>
       <c r="C61" s="126"/>
@@ -5134,7 +5142,7 @@
       <c r="I61" s="129"/>
       <c r="J61" s="129"/>
     </row>
-    <row r="62" spans="1:10" ht="12.75">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="126"/>
       <c r="B62" s="126"/>
       <c r="C62" s="126"/>
@@ -5146,7 +5154,7 @@
       <c r="I62" s="129"/>
       <c r="J62" s="129"/>
     </row>
-    <row r="63" spans="1:10" ht="15" customHeight="1">
+    <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="46"/>
       <c r="B63" s="46"/>
       <c r="G63" s="40"/>
@@ -5154,35 +5162,35 @@
       <c r="I63" s="65"/>
       <c r="J63" s="65"/>
     </row>
-    <row r="64" spans="1:10" ht="12.75">
+    <row r="64" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="5"/>
       <c r="D64" s="6"/>
       <c r="E64" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F64" s="8">
         <v>152</v>
       </c>
       <c r="H64" s="40"/>
     </row>
-    <row r="65" spans="1:8" ht="12.75">
+    <row r="65" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="9"/>
       <c r="D65" s="2"/>
       <c r="E65" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F65" s="11">
         <v>19</v>
       </c>
       <c r="H65" s="40"/>
     </row>
-    <row r="66" spans="1:8" ht="14.25">
+    <row r="66" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A66" s="130" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B66" s="130"/>
       <c r="C66" s="130"/>
@@ -5191,13 +5199,13 @@
       <c r="F66" s="2"/>
       <c r="H66" s="40"/>
     </row>
-    <row r="67" spans="1:8" ht="14.25">
+    <row r="67" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A67" s="13"/>
       <c r="B67" s="13"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F67" s="15">
         <f>SUMIF(F9:F59,"Billable",H9:H59)</f>
@@ -5205,37 +5213,37 @@
       </c>
       <c r="H67" s="38"/>
     </row>
-    <row r="68" spans="1:8" ht="14.25">
+    <row r="68" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A68" s="131" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B68" s="131"/>
       <c r="C68" s="131"/>
       <c r="D68" s="16"/>
       <c r="E68" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F68" s="18">
         <f>SUMIF(F9:F59,"Non-Billable",H9:H59)</f>
-        <v>7.4402777777777791</v>
+        <v>7.7180555555555559</v>
       </c>
       <c r="H68" s="40"/>
     </row>
-    <row r="69" spans="1:8" ht="14.25">
+    <row r="69" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F69" s="44">
         <f>F67+F68</f>
-        <v>7.4402777777777791</v>
+        <v>7.7180555555555559</v>
       </c>
       <c r="H69" s="40"/>
     </row>
-    <row r="70" spans="1:8" ht="12.75">
+    <row r="70" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -5244,18 +5252,18 @@
       <c r="F70" s="2"/>
       <c r="H70" s="40"/>
     </row>
-    <row r="71" spans="1:8" ht="12.75">
+    <row r="71" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F71" s="21"/>
       <c r="H71" s="40"/>
     </row>
-    <row r="72" spans="1:8" ht="12.75">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="E72" s="39"/>
       <c r="H72" s="40"/>
     </row>
@@ -5266,56 +5274,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D7:E7">
-    <cfRule type="containsText" dxfId="102" priority="12" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="95" priority="12" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="101" priority="13" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="94" priority="13" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="100" priority="14" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="93" priority="14" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="99" priority="15" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="92" priority="15" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="98" priority="16" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="91" priority="16" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="97" priority="17" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="90" priority="17" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="18" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B63:B72 B8:B53">
-    <cfRule type="containsText" dxfId="95" priority="1" operator="containsText" text="Saturday">
+  <conditionalFormatting sqref="B8:B53 B63:B72">
+    <cfRule type="containsText" dxfId="88" priority="1" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="94" priority="2" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="87" priority="2" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D64:E64 D66:E68 E71">
-    <cfRule type="containsText" dxfId="93" priority="3" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="86" priority="3" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D64)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="92" priority="4" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="85" priority="4" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D64)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="91" priority="5" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="84" priority="5" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D64)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="90" priority="6" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="83" priority="6" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D64)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="89" priority="7" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="82" priority="7" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D64)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="88" priority="8" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="81" priority="8" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D64)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="9" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5364,28 +5372,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451FE93A-CBFB-4D27-9D4A-1E2332DAE6F0}">
   <dimension ref="A5:J49"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -5399,10 +5407,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -5434,7 +5442,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="47">
         <v>46143</v>
       </c>
@@ -5452,7 +5460,7 @@
         <v>16</v>
       </c>
       <c r="G9" s="49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H9" s="50">
         <f t="shared" ref="H9:H39" si="0">J9-I9</f>
@@ -5465,7 +5473,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="31">
         <v>46144</v>
       </c>
@@ -5484,7 +5492,7 @@
       <c r="I10" s="35"/>
       <c r="J10" s="35"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="31">
         <v>46145</v>
       </c>
@@ -5503,7 +5511,7 @@
       <c r="I11" s="35"/>
       <c r="J11" s="35"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>46146</v>
       </c>
@@ -5514,16 +5522,16 @@
         <v>14</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E12" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="G12" s="28" t="s">
         <v>71</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>72</v>
       </c>
       <c r="H12" s="29">
         <f t="shared" si="0"/>
@@ -5536,7 +5544,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>46147</v>
       </c>
@@ -5555,7 +5563,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
         <v>46148</v>
       </c>
@@ -5574,7 +5582,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="22">
         <v>46149</v>
       </c>
@@ -5593,7 +5601,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>46150</v>
       </c>
@@ -5612,7 +5620,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="31">
         <v>46151</v>
       </c>
@@ -5631,7 +5639,7 @@
       <c r="I17" s="35"/>
       <c r="J17" s="35"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="31">
         <v>46152</v>
       </c>
@@ -5650,7 +5658,7 @@
       <c r="I18" s="35"/>
       <c r="J18" s="35"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="22">
         <v>46153</v>
       </c>
@@ -5669,7 +5677,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="22">
         <v>46154</v>
       </c>
@@ -5688,7 +5696,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="22">
         <v>46155</v>
       </c>
@@ -5707,7 +5715,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="22">
         <v>46156</v>
       </c>
@@ -5726,7 +5734,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="22">
         <v>46157</v>
       </c>
@@ -5745,7 +5753,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="31">
         <v>46158</v>
       </c>
@@ -5764,7 +5772,7 @@
       <c r="I24" s="35"/>
       <c r="J24" s="35"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="31">
         <v>46159</v>
       </c>
@@ -5783,7 +5791,7 @@
       <c r="I25" s="35"/>
       <c r="J25" s="35"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="22">
         <v>46160</v>
       </c>
@@ -5802,7 +5810,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="22">
         <v>46161</v>
       </c>
@@ -5821,7 +5829,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="22">
         <v>46162</v>
       </c>
@@ -5840,7 +5848,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="22">
         <v>46163</v>
       </c>
@@ -5859,7 +5867,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
         <v>46164</v>
       </c>
@@ -5878,7 +5886,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="31">
         <v>46165</v>
       </c>
@@ -5897,7 +5905,7 @@
       <c r="I31" s="35"/>
       <c r="J31" s="35"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="31">
         <v>46166</v>
       </c>
@@ -5916,7 +5924,7 @@
       <c r="I32" s="35"/>
       <c r="J32" s="35"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>46167</v>
       </c>
@@ -5935,7 +5943,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="22">
         <v>46168</v>
       </c>
@@ -5954,7 +5962,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>46169</v>
       </c>
@@ -5973,7 +5981,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>46170</v>
       </c>
@@ -5992,7 +6000,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>46171</v>
       </c>
@@ -6011,7 +6019,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="31">
         <v>46172</v>
       </c>
@@ -6030,7 +6038,7 @@
       <c r="I38" s="35"/>
       <c r="J38" s="35"/>
     </row>
-    <row r="39" spans="1:10" ht="13.9" customHeight="1">
+    <row r="39" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="31">
         <v>46173</v>
       </c>
@@ -6049,7 +6057,7 @@
       <c r="I39" s="98"/>
       <c r="J39" s="32"/>
     </row>
-    <row r="40" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="40" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="46"/>
       <c r="B40" s="45"/>
       <c r="C40" s="45"/>
@@ -6060,35 +6068,35 @@
       <c r="H40" s="36"/>
       <c r="I40" s="37"/>
     </row>
-    <row r="41" spans="1:10" ht="13.9" customHeight="1">
+    <row r="41" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
       <c r="D41" s="6"/>
       <c r="E41" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F41" s="8">
         <v>160</v>
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="9"/>
       <c r="D42" s="2"/>
       <c r="E42" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F42" s="11">
         <v>20</v>
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="43" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="130" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" s="130"/>
       <c r="C43" s="130"/>
@@ -6097,13 +6105,13 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.9">
+    <row r="44" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F44" s="15">
         <f>SUMIF(F9:F39,"Billable",H9:H39)</f>
@@ -6111,15 +6119,15 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="131" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45" s="131"/>
       <c r="C45" s="131"/>
       <c r="D45" s="16"/>
       <c r="E45" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F45" s="18">
         <f>SUMIF(F9:F39,"Non-Billable",H9:H39)</f>
@@ -6127,13 +6135,13 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.45" thickBot="1">
+    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F46" s="44">
         <f>F44+F45</f>
@@ -6141,7 +6149,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1">
+    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -6150,18 +6158,18 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.9" thickBot="1">
+    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.15" thickBot="1">
+    <row r="49" spans="5:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -6172,56 +6180,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="86" priority="21" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="79" priority="21" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="85" priority="22" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="78" priority="22" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="84" priority="23" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="77" priority="23" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="83" priority="24" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="76" priority="24" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="82" priority="25" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="75" priority="25" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="81" priority="26" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="74" priority="26" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="27" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B49">
-    <cfRule type="containsText" dxfId="79" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="72" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="71" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39:E41 D43:E45 E48">
-    <cfRule type="containsText" dxfId="77" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="70" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="69" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="75" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="68" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="74" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="67" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="73" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="66" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="65" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6273,28 +6281,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738C92ED-F226-4107-8C14-FCA383B998C3}">
   <dimension ref="A5:J48"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -6308,10 +6316,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -6343,7 +6351,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="22">
         <v>46174</v>
       </c>
@@ -6354,16 +6362,16 @@
         <v>14</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="G9" s="28" t="s">
         <v>71</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>72</v>
       </c>
       <c r="H9" s="29">
         <f t="shared" ref="H9" si="0">J9-I9</f>
@@ -6376,7 +6384,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>46175</v>
       </c>
@@ -6395,7 +6403,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46176</v>
       </c>
@@ -6414,7 +6422,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>46177</v>
       </c>
@@ -6433,7 +6441,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>46178</v>
       </c>
@@ -6452,7 +6460,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="31">
         <v>46179</v>
       </c>
@@ -6471,7 +6479,7 @@
       <c r="I14" s="35"/>
       <c r="J14" s="35"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="31">
         <v>46180</v>
       </c>
@@ -6490,7 +6498,7 @@
       <c r="I15" s="35"/>
       <c r="J15" s="35"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>46181</v>
       </c>
@@ -6509,7 +6517,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="22">
         <v>46182</v>
       </c>
@@ -6528,7 +6536,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="22">
         <v>46183</v>
       </c>
@@ -6547,7 +6555,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="22">
         <v>46184</v>
       </c>
@@ -6566,7 +6574,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="22">
         <v>46185</v>
       </c>
@@ -6585,7 +6593,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="31">
         <v>46186</v>
       </c>
@@ -6604,7 +6612,7 @@
       <c r="I21" s="35"/>
       <c r="J21" s="35"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="31">
         <v>46187</v>
       </c>
@@ -6623,7 +6631,7 @@
       <c r="I22" s="35"/>
       <c r="J22" s="35"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="22">
         <v>46188</v>
       </c>
@@ -6642,7 +6650,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="47">
         <v>46189</v>
       </c>
@@ -6660,7 +6668,7 @@
         <v>16</v>
       </c>
       <c r="G24" s="49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H24" s="50">
         <f t="shared" si="1"/>
@@ -6673,7 +6681,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="22">
         <v>46190</v>
       </c>
@@ -6692,7 +6700,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="22">
         <v>46191</v>
       </c>
@@ -6711,7 +6719,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="22">
         <v>46192</v>
       </c>
@@ -6730,7 +6738,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="31">
         <v>46193</v>
       </c>
@@ -6749,7 +6757,7 @@
       <c r="I28" s="35"/>
       <c r="J28" s="35"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="31">
         <v>46194</v>
       </c>
@@ -6768,7 +6776,7 @@
       <c r="I29" s="35"/>
       <c r="J29" s="35"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
         <v>46195</v>
       </c>
@@ -6787,7 +6795,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="22">
         <v>46196</v>
       </c>
@@ -6806,7 +6814,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="22">
         <v>46197</v>
       </c>
@@ -6825,7 +6833,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>46198</v>
       </c>
@@ -6844,7 +6852,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="22">
         <v>46199</v>
       </c>
@@ -6863,7 +6871,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="31">
         <v>46200</v>
       </c>
@@ -6882,7 +6890,7 @@
       <c r="I35" s="35"/>
       <c r="J35" s="35"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="31">
         <v>46201</v>
       </c>
@@ -6901,7 +6909,7 @@
       <c r="I36" s="35"/>
       <c r="J36" s="35"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>46202</v>
       </c>
@@ -6920,7 +6928,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10" ht="13.15" thickBot="1">
+    <row r="38" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="22">
         <v>46203</v>
       </c>
@@ -6939,7 +6947,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="39" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="45"/>
       <c r="B39" s="45"/>
       <c r="C39" s="45"/>
@@ -6950,35 +6958,35 @@
       <c r="H39" s="36"/>
       <c r="I39" s="37"/>
     </row>
-    <row r="40" spans="1:10" ht="13.9" customHeight="1">
+    <row r="40" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
       <c r="D40" s="6"/>
       <c r="E40" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F40" s="8">
         <v>168</v>
       </c>
       <c r="H40" s="40"/>
     </row>
-    <row r="41" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="41" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="9"/>
       <c r="D41" s="2"/>
       <c r="E41" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F41" s="11">
         <v>21</v>
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="130" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B42" s="130"/>
       <c r="C42" s="130"/>
@@ -6987,13 +6995,13 @@
       <c r="F42" s="2"/>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.9">
+    <row r="43" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="13"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F43" s="15">
         <f>SUMIF(F9:F38,"Billable",H9:H38)</f>
@@ -7001,15 +7009,15 @@
       </c>
       <c r="H43" s="38"/>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1">
+    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="131" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B44" s="131"/>
       <c r="C44" s="131"/>
       <c r="D44" s="16"/>
       <c r="E44" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F44" s="18">
         <f>SUMIF(F9:F38,"Non-Billable",H9:H38)</f>
@@ -7017,13 +7025,13 @@
       </c>
       <c r="H44" s="40"/>
     </row>
-    <row r="45" spans="1:10" ht="14.45" thickBot="1">
+    <row r="45" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F45" s="44">
         <f>F43+F44</f>
@@ -7031,7 +7039,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="13.9" thickBot="1">
+    <row r="46" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -7040,18 +7048,18 @@
       <c r="F46" s="2"/>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1">
+    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F47" s="21"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.15" thickBot="1">
+    <row r="48" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E48" s="39"/>
       <c r="H48" s="40"/>
     </row>
@@ -7062,56 +7070,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="70" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="63" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="69" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="62" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="61" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="67" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="60" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="59" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="65" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="58" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B48">
-    <cfRule type="containsText" dxfId="63" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="56" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="55" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39:E40 D42:E44 E47">
-    <cfRule type="containsText" dxfId="61" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="54" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="53" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="59" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="52" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="51" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="50" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="49" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7169,28 +7177,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4077AC14-6A48-4DDF-A891-D5BFFE7E5F3C}">
   <dimension ref="A5:J49"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -7204,10 +7212,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -7239,7 +7247,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="22">
         <v>46204</v>
       </c>
@@ -7250,16 +7258,16 @@
         <v>14</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="G9" s="28" t="s">
         <v>71</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>72</v>
       </c>
       <c r="H9" s="29">
         <f>J9-I9</f>
@@ -7272,7 +7280,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>46205</v>
       </c>
@@ -7291,7 +7299,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46206</v>
       </c>
@@ -7310,7 +7318,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="31">
         <v>46207</v>
       </c>
@@ -7329,7 +7337,7 @@
       <c r="I12" s="35"/>
       <c r="J12" s="35"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="31">
         <v>46208</v>
       </c>
@@ -7348,7 +7356,7 @@
       <c r="I13" s="35"/>
       <c r="J13" s="35"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
         <v>46209</v>
       </c>
@@ -7367,7 +7375,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="22">
         <v>46210</v>
       </c>
@@ -7386,7 +7394,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>46211</v>
       </c>
@@ -7405,7 +7413,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="22">
         <v>46212</v>
       </c>
@@ -7424,7 +7432,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="22">
         <v>46213</v>
       </c>
@@ -7443,7 +7451,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="31">
         <v>46214</v>
       </c>
@@ -7462,7 +7470,7 @@
       <c r="I19" s="35"/>
       <c r="J19" s="35"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="31">
         <v>46215</v>
       </c>
@@ -7481,7 +7489,7 @@
       <c r="I20" s="35"/>
       <c r="J20" s="35"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="22">
         <v>46216</v>
       </c>
@@ -7500,7 +7508,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="22">
         <v>46217</v>
       </c>
@@ -7519,7 +7527,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="22">
         <v>46218</v>
       </c>
@@ -7538,7 +7546,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="22">
         <v>46219</v>
       </c>
@@ -7557,7 +7565,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="22">
         <v>46220</v>
       </c>
@@ -7576,7 +7584,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="31">
         <v>46221</v>
       </c>
@@ -7595,7 +7603,7 @@
       <c r="I26" s="35"/>
       <c r="J26" s="35"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="31">
         <v>46222</v>
       </c>
@@ -7614,7 +7622,7 @@
       <c r="I27" s="35"/>
       <c r="J27" s="35"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="22">
         <v>46223</v>
       </c>
@@ -7633,7 +7641,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="22">
         <v>46224</v>
       </c>
@@ -7652,7 +7660,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
         <v>46225</v>
       </c>
@@ -7671,7 +7679,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="22">
         <v>46226</v>
       </c>
@@ -7690,7 +7698,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="22">
         <v>46227</v>
       </c>
@@ -7709,7 +7717,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="31">
         <v>46228</v>
       </c>
@@ -7728,7 +7736,7 @@
       <c r="I33" s="35"/>
       <c r="J33" s="35"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="31">
         <v>46229</v>
       </c>
@@ -7747,7 +7755,7 @@
       <c r="I34" s="35"/>
       <c r="J34" s="35"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>46230</v>
       </c>
@@ -7766,7 +7774,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>46231</v>
       </c>
@@ -7785,7 +7793,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>46232</v>
       </c>
@@ -7804,7 +7812,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="22">
         <v>46233</v>
       </c>
@@ -7823,7 +7831,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" ht="13.15" thickBot="1">
+    <row r="39" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="22">
         <v>46234</v>
       </c>
@@ -7842,7 +7850,7 @@
       <c r="I39" s="30"/>
       <c r="J39" s="30"/>
     </row>
-    <row r="40" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="40" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -7853,35 +7861,35 @@
       <c r="H40" s="36"/>
       <c r="I40" s="37"/>
     </row>
-    <row r="41" spans="1:10" ht="13.9" customHeight="1">
+    <row r="41" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
       <c r="D41" s="6"/>
       <c r="E41" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F41" s="8">
         <v>184</v>
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="9"/>
       <c r="D42" s="2"/>
       <c r="E42" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F42" s="11">
         <v>23</v>
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="43" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="130" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" s="130"/>
       <c r="C43" s="130"/>
@@ -7890,13 +7898,13 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.9">
+    <row r="44" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F44" s="15">
         <f>SUMIF(F9:F39,"Billable",H9:H39)</f>
@@ -7904,15 +7912,15 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="131" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45" s="131"/>
       <c r="C45" s="131"/>
       <c r="D45" s="16"/>
       <c r="E45" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F45" s="18">
         <f>SUMIF(F9:F39,"Non-Billable",H9:H39)</f>
@@ -7920,13 +7928,13 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.45" thickBot="1">
+    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F46" s="44">
         <f>F44+F45</f>
@@ -7934,7 +7942,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1">
+    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -7943,18 +7951,18 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.9" thickBot="1">
+    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.15" thickBot="1">
+    <row r="49" spans="5:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -7965,56 +7973,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="54" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="47" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="53" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="46" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="45" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="44" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="43" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="49" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="42" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B49">
-    <cfRule type="containsText" dxfId="47" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="40" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="39" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E41 D43:E45 E48">
-    <cfRule type="containsText" dxfId="45" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="38" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="37" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="35" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="41" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="33" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8076,28 +8084,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F5FF808-4CDC-4429-9978-CAD26FE6591A}">
   <dimension ref="A5:J49"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -8111,10 +8119,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -8146,7 +8154,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="31">
         <v>46235</v>
       </c>
@@ -8165,7 +8173,7 @@
       <c r="I9" s="35"/>
       <c r="J9" s="35"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="31">
         <v>46236</v>
       </c>
@@ -8184,7 +8192,7 @@
       <c r="I10" s="35"/>
       <c r="J10" s="35"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46237</v>
       </c>
@@ -8195,16 +8203,16 @@
         <v>14</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E11" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="G11" s="28" t="s">
         <v>71</v>
-      </c>
-      <c r="G11" s="28" t="s">
-        <v>72</v>
       </c>
       <c r="H11" s="29">
         <f t="shared" ref="H11" si="1">J11-I11</f>
@@ -8217,7 +8225,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>46238</v>
       </c>
@@ -8236,7 +8244,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>46239</v>
       </c>
@@ -8255,7 +8263,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
         <v>46240</v>
       </c>
@@ -8274,7 +8282,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="22">
         <v>46241</v>
       </c>
@@ -8293,7 +8301,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="31">
         <v>46242</v>
       </c>
@@ -8312,7 +8320,7 @@
       <c r="I16" s="35"/>
       <c r="J16" s="35"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="31">
         <v>46243</v>
       </c>
@@ -8324,7 +8332,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
       <c r="G17" s="33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H17" s="34">
         <f t="shared" si="2"/>
@@ -8333,7 +8341,7 @@
       <c r="I17" s="35"/>
       <c r="J17" s="35"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="47">
         <v>46244</v>
       </c>
@@ -8351,7 +8359,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H18" s="50">
         <f t="shared" si="2"/>
@@ -8364,7 +8372,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="22">
         <v>46245</v>
       </c>
@@ -8383,7 +8391,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="22">
         <v>46246</v>
       </c>
@@ -8402,7 +8410,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="22">
         <v>46247</v>
       </c>
@@ -8421,7 +8429,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="22">
         <v>46248</v>
       </c>
@@ -8440,7 +8448,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="31">
         <v>46249</v>
       </c>
@@ -8459,7 +8467,7 @@
       <c r="I23" s="35"/>
       <c r="J23" s="35"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="31">
         <v>46250</v>
       </c>
@@ -8478,7 +8486,7 @@
       <c r="I24" s="35"/>
       <c r="J24" s="35"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="22">
         <v>46251</v>
       </c>
@@ -8497,7 +8505,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="22">
         <v>46252</v>
       </c>
@@ -8516,7 +8524,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="22">
         <v>46253</v>
       </c>
@@ -8535,7 +8543,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="22">
         <v>46254</v>
       </c>
@@ -8554,7 +8562,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="22">
         <v>46255</v>
       </c>
@@ -8573,7 +8581,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="31">
         <v>46256</v>
       </c>
@@ -8592,7 +8600,7 @@
       <c r="I30" s="35"/>
       <c r="J30" s="35"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="31">
         <v>46257</v>
       </c>
@@ -8611,7 +8619,7 @@
       <c r="I31" s="35"/>
       <c r="J31" s="35"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="22">
         <v>46258</v>
       </c>
@@ -8630,7 +8638,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>46259</v>
       </c>
@@ -8649,7 +8657,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="22">
         <v>46260</v>
       </c>
@@ -8668,7 +8676,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>46261</v>
       </c>
@@ -8687,7 +8695,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>46262</v>
       </c>
@@ -8706,7 +8714,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="31">
         <v>46263</v>
       </c>
@@ -8725,7 +8733,7 @@
       <c r="I37" s="35"/>
       <c r="J37" s="35"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="31">
         <v>46264</v>
       </c>
@@ -8744,7 +8752,7 @@
       <c r="I38" s="35"/>
       <c r="J38" s="35"/>
     </row>
-    <row r="39" spans="1:10" ht="13.9" customHeight="1">
+    <row r="39" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="22">
         <v>46265</v>
       </c>
@@ -8763,7 +8771,7 @@
       <c r="I39" s="30"/>
       <c r="J39" s="30"/>
     </row>
-    <row r="40" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="40" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="46"/>
       <c r="B40" s="45"/>
       <c r="C40" s="45"/>
@@ -8774,35 +8782,35 @@
       <c r="H40" s="36"/>
       <c r="I40" s="37"/>
     </row>
-    <row r="41" spans="1:10" ht="13.9" customHeight="1">
+    <row r="41" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
       <c r="D41" s="6"/>
       <c r="E41" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F41" s="8">
         <v>160</v>
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="9"/>
       <c r="D42" s="2"/>
       <c r="E42" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F42" s="11">
         <v>20</v>
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="43" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="130" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" s="130"/>
       <c r="C43" s="130"/>
@@ -8811,13 +8819,13 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.9">
+    <row r="44" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F44" s="15">
         <f>SUMIF(F9:F39,"Billable",H9:H39)</f>
@@ -8825,15 +8833,15 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="131" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45" s="131"/>
       <c r="C45" s="131"/>
       <c r="D45" s="16"/>
       <c r="E45" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F45" s="18">
         <f>SUMIF(F9:F39,"Non-Billable",H9:H39)</f>
@@ -8841,13 +8849,13 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.45" thickBot="1">
+    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F46" s="44">
         <f>F44+F45</f>
@@ -8855,7 +8863,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1">
+    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -8864,18 +8872,18 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.9" thickBot="1">
+    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.15" thickBot="1">
+    <row r="49" spans="5:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -8886,56 +8894,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="38" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="31" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="30" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="29" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="35" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="28" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="27" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="26" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B49">
-    <cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="24" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="23" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E41 D43:E45 E48">
-    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="19" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8987,28 +8995,28 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D1366D5-46F5-410C-BC9F-D56DCF566D28}">
   <dimension ref="A5:J48"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -9022,10 +9030,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -9057,7 +9065,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="22">
         <v>46266</v>
       </c>
@@ -9068,16 +9076,16 @@
         <v>14</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="G9" s="28" t="s">
         <v>71</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>72</v>
       </c>
       <c r="H9" s="29">
         <f t="shared" ref="H9" si="0">J9-I9</f>
@@ -9090,7 +9098,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>46267</v>
       </c>
@@ -9109,7 +9117,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46268</v>
       </c>
@@ -9128,7 +9136,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>46269</v>
       </c>
@@ -9147,7 +9155,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="31">
         <v>46270</v>
       </c>
@@ -9166,7 +9174,7 @@
       <c r="I13" s="35"/>
       <c r="J13" s="35"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="31">
         <v>46271</v>
       </c>
@@ -9185,7 +9193,7 @@
       <c r="I14" s="35"/>
       <c r="J14" s="35"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="22">
         <v>46272</v>
       </c>
@@ -9204,7 +9212,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>46273</v>
       </c>
@@ -9223,7 +9231,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="22">
         <v>46274</v>
       </c>
@@ -9242,7 +9250,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="22">
         <v>46275</v>
       </c>
@@ -9261,7 +9269,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="22">
         <v>46276</v>
       </c>
@@ -9280,7 +9288,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="31">
         <v>46277</v>
       </c>
@@ -9299,7 +9307,7 @@
       <c r="I20" s="35"/>
       <c r="J20" s="35"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="31">
         <v>46278</v>
       </c>
@@ -9318,7 +9326,7 @@
       <c r="I21" s="35"/>
       <c r="J21" s="35"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="22">
         <v>46279</v>
       </c>
@@ -9337,7 +9345,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="22">
         <v>46280</v>
       </c>
@@ -9356,7 +9364,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="22">
         <v>46281</v>
       </c>
@@ -9375,7 +9383,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="22">
         <v>46282</v>
       </c>
@@ -9394,7 +9402,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="22">
         <v>46283</v>
       </c>
@@ -9413,7 +9421,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="31">
         <v>46284</v>
       </c>
@@ -9432,7 +9440,7 @@
       <c r="I27" s="35"/>
       <c r="J27" s="35"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="31">
         <v>46285</v>
       </c>
@@ -9451,7 +9459,7 @@
       <c r="I28" s="35"/>
       <c r="J28" s="35"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="22">
         <v>46286</v>
       </c>
@@ -9470,7 +9478,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
         <v>46287</v>
       </c>
@@ -9489,7 +9497,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="22">
         <v>46288</v>
       </c>
@@ -9508,7 +9516,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="47">
         <v>46289</v>
       </c>
@@ -9526,7 +9534,7 @@
         <v>16</v>
       </c>
       <c r="G32" s="49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H32" s="50">
         <f t="shared" ref="H32" si="2">J32-I32</f>
@@ -9539,7 +9547,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>46290</v>
       </c>
@@ -9558,7 +9566,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="31">
         <v>46291</v>
       </c>
@@ -9577,7 +9585,7 @@
       <c r="I34" s="35"/>
       <c r="J34" s="35"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="31">
         <v>46292</v>
       </c>
@@ -9596,7 +9604,7 @@
       <c r="I35" s="35"/>
       <c r="J35" s="35"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>46293</v>
       </c>
@@ -9615,7 +9623,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>46294</v>
       </c>
@@ -9634,7 +9642,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="22">
         <v>46295</v>
       </c>
@@ -9653,7 +9661,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="39" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="46"/>
       <c r="B39" s="46"/>
       <c r="C39" s="45"/>
@@ -9664,35 +9672,35 @@
       <c r="H39" s="36"/>
       <c r="I39" s="37"/>
     </row>
-    <row r="40" spans="1:10" ht="13.9" customHeight="1">
+    <row r="40" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
       <c r="D40" s="6"/>
       <c r="E40" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F40" s="8">
         <v>168</v>
       </c>
       <c r="H40" s="40"/>
     </row>
-    <row r="41" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="41" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="9"/>
       <c r="D41" s="2"/>
       <c r="E41" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F41" s="11">
         <v>21</v>
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="130" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B42" s="130"/>
       <c r="C42" s="130"/>
@@ -9701,13 +9709,13 @@
       <c r="F42" s="2"/>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.9">
+    <row r="43" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="13"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F43" s="15">
         <f>SUMIF(F9:F38,"Billable",H9:H38)</f>
@@ -9715,15 +9723,15 @@
       </c>
       <c r="H43" s="38"/>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1">
+    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="131" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B44" s="131"/>
       <c r="C44" s="131"/>
       <c r="D44" s="16"/>
       <c r="E44" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F44" s="18">
         <f>SUMIF(F9:F38,"Non-Billable",H9:H38)</f>
@@ -9731,13 +9739,13 @@
       </c>
       <c r="H44" s="40"/>
     </row>
-    <row r="45" spans="1:10" ht="14.45" thickBot="1">
+    <row r="45" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F45" s="44">
         <f>F43+F44</f>
@@ -9745,7 +9753,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="13.9" thickBot="1">
+    <row r="46" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -9754,18 +9762,18 @@
       <c r="F46" s="2"/>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1">
+    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F47" s="21"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.15" thickBot="1">
+    <row r="48" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E48" s="39"/>
       <c r="H48" s="40"/>
     </row>
@@ -9776,56 +9784,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7 D39:E40">
-    <cfRule type="containsText" dxfId="22" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="15" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="13" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="12" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="11" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B48">
-    <cfRule type="containsText" dxfId="15" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42:E44 E47">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9893,18 +9901,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{368E8809-782A-4EC8-A7EE-23E6EB29126F}">
   <dimension ref="A1:O18"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.75" style="23"/>
-    <col min="5" max="5" width="13.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69921875" style="23"/>
+    <col min="5" max="5" width="13.19921875" style="23" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="23" customWidth="1"/>
-    <col min="7" max="16384" width="8.75" style="23"/>
+    <col min="7" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="13.5" customHeight="1">
+    <row r="1" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="80"/>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -9912,7 +9920,7 @@
       <c r="E1" s="80"/>
       <c r="F1" s="80"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="79"/>
       <c r="B2" s="79"/>
       <c r="C2" s="84"/>
@@ -9920,7 +9928,7 @@
       <c r="E2" s="84"/>
       <c r="F2" s="84"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="79"/>
       <c r="B3" s="79"/>
       <c r="C3" s="85"/>
@@ -9928,7 +9936,7 @@
       <c r="E3" s="85"/>
       <c r="F3" s="85"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="79"/>
       <c r="B4" s="79"/>
       <c r="C4" s="86"/>
@@ -9936,21 +9944,21 @@
       <c r="E4" s="86"/>
       <c r="F4" s="86"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" s="86"/>
       <c r="D5" s="86"/>
       <c r="E5" s="86"/>
       <c r="F5" s="86"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="79" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B6" s="81">
         <f>F17</f>
@@ -9961,7 +9969,7 @@
       <c r="E6" s="85"/>
       <c r="F6" s="85"/>
     </row>
-    <row r="7" spans="1:15" ht="13.5" customHeight="1">
+    <row r="7" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="73"/>
       <c r="B7" s="74"/>
       <c r="C7" s="74"/>
@@ -9969,139 +9977,139 @@
       <c r="E7" s="85"/>
       <c r="F7" s="85"/>
     </row>
-    <row r="8" spans="1:15" ht="27.4" customHeight="1">
-      <c r="A8" s="140" t="s">
+    <row r="8" spans="1:15" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="137" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="137"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="137"/>
+    </row>
+    <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="140"/>
-      <c r="C8" s="140"/>
-      <c r="D8" s="140"/>
-      <c r="E8" s="140"/>
-      <c r="F8" s="140"/>
-    </row>
-    <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A9" s="82" t="s">
+      <c r="B9" s="134" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="143" t="s">
+      <c r="C9" s="135"/>
+      <c r="D9" s="134" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="144"/>
-      <c r="D9" s="143" t="s">
+      <c r="E9" s="135"/>
+      <c r="F9" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="144"/>
-      <c r="F9" s="83" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="78">
         <v>46113</v>
       </c>
-      <c r="B10" s="134" t="s">
+      <c r="B10" s="136" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="136"/>
+      <c r="D10" s="136" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="134"/>
-      <c r="D10" s="134" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="134"/>
+      <c r="E10" s="136"/>
       <c r="F10" s="77">
         <v>200</v>
       </c>
-      <c r="G10" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="H10" s="142"/>
-      <c r="I10" s="142"/>
-      <c r="J10" s="142"/>
-      <c r="K10" s="142"/>
-      <c r="L10" s="142"/>
-      <c r="M10" s="142"/>
-      <c r="N10" s="142"/>
-      <c r="O10" s="142"/>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="G10" s="132" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="133"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133"/>
+      <c r="K10" s="133"/>
+      <c r="L10" s="133"/>
+      <c r="M10" s="133"/>
+      <c r="N10" s="133"/>
+      <c r="O10" s="133"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="78">
         <v>46113</v>
       </c>
-      <c r="B11" s="132" t="s">
+      <c r="B11" s="138" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="139"/>
+      <c r="D11" s="136" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="133"/>
-      <c r="D11" s="134" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" s="134"/>
+      <c r="E11" s="136"/>
       <c r="F11" s="77"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="78">
         <v>46113</v>
       </c>
-      <c r="B12" s="132" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="133"/>
-      <c r="D12" s="134"/>
-      <c r="E12" s="134"/>
+      <c r="B12" s="138" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="139"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
       <c r="F12" s="77"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="78">
         <v>46113</v>
       </c>
-      <c r="B13" s="132"/>
-      <c r="C13" s="133"/>
-      <c r="D13" s="134"/>
-      <c r="E13" s="134"/>
+      <c r="B13" s="138"/>
+      <c r="C13" s="139"/>
+      <c r="D13" s="136"/>
+      <c r="E13" s="136"/>
       <c r="F13" s="77"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="78">
         <v>46113</v>
       </c>
-      <c r="B14" s="132"/>
-      <c r="C14" s="133"/>
-      <c r="D14" s="134"/>
-      <c r="E14" s="134"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="139"/>
+      <c r="D14" s="136"/>
+      <c r="E14" s="136"/>
       <c r="F14" s="77"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="78">
         <v>46113</v>
       </c>
-      <c r="B15" s="138"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="134"/>
-      <c r="E15" s="134"/>
+      <c r="B15" s="143"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="136"/>
+      <c r="E15" s="136"/>
       <c r="F15" s="77"/>
     </row>
-    <row r="16" spans="1:15" ht="13.15" thickBot="1">
+    <row r="16" spans="1:15" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78">
         <v>46113</v>
       </c>
-      <c r="B16" s="132"/>
-      <c r="C16" s="133"/>
-      <c r="D16" s="134"/>
-      <c r="E16" s="134"/>
+      <c r="B16" s="138"/>
+      <c r="C16" s="139"/>
+      <c r="D16" s="136"/>
+      <c r="E16" s="136"/>
       <c r="F16" s="77"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A17" s="135" t="s">
-        <v>89</v>
-      </c>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="137"/>
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="140" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="141"/>
+      <c r="C17" s="141"/>
+      <c r="D17" s="141"/>
+      <c r="E17" s="142"/>
       <c r="F17" s="76">
         <f>SUM(F10:F16)</f>
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="73"/>
       <c r="B18" s="74"/>
       <c r="C18" s="74"/>
@@ -10111,16 +10119,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -10130,6 +10128,16 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -10159,45 +10167,45 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0517D5F3-AC91-43ED-96BB-0299CBED5EE0}">
   <dimension ref="A4:F23"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.75" style="23" customWidth="1"/>
-    <col min="3" max="3" width="9.75" style="23" customWidth="1"/>
-    <col min="4" max="16384" width="8.75" style="23"/>
+    <col min="2" max="2" width="11.69921875" style="23" customWidth="1"/>
+    <col min="3" max="3" width="9.69921875" style="23" customWidth="1"/>
+    <col min="4" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="145"/>
       <c r="B4" s="145"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="79" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="79"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="79"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="95" t="s">
-        <v>91</v>
-      </c>
       <c r="B7" s="95"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="96"/>
       <c r="B8" s="85"/>
     </row>
-    <row r="9" spans="1:6" ht="27.4" customHeight="1">
+    <row r="9" spans="1:6" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="158" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" s="158"/>
       <c r="C9" s="158"/>
@@ -10205,39 +10213,39 @@
       <c r="E9" s="158"/>
       <c r="F9" s="158"/>
     </row>
-    <row r="10" spans="1:6" ht="25.15">
+    <row r="10" spans="1:6" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A10" s="87" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="87" t="s">
+      <c r="C10" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="87" t="s">
+      <c r="D10" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="87" t="s">
+      <c r="E10" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="E10" s="87" t="s">
+      <c r="F10" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="F10" s="87" t="s">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="87" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="87" t="s">
-        <v>99</v>
       </c>
       <c r="B11" s="117"/>
       <c r="C11" s="117"/>
       <c r="D11" s="87"/>
       <c r="E11" s="87"/>
       <c r="F11" s="87" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="87"/>
       <c r="B12" s="87"/>
       <c r="C12" s="87"/>
@@ -10245,7 +10253,7 @@
       <c r="E12" s="87"/>
       <c r="F12" s="87"/>
     </row>
-    <row r="13" spans="1:6" ht="13.15" thickBot="1">
+    <row r="13" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="87"/>
       <c r="B13" s="87"/>
       <c r="C13" s="87"/>
@@ -10253,7 +10261,7 @@
       <c r="E13" s="87"/>
       <c r="F13" s="87"/>
     </row>
-    <row r="14" spans="1:6" ht="13.15" thickBot="1">
+    <row r="14" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="88"/>
       <c r="B14" s="89"/>
       <c r="C14" s="89"/>
@@ -10264,7 +10272,7 @@
       <c r="E14" s="89"/>
       <c r="F14" s="91"/>
     </row>
-    <row r="15" spans="1:6" ht="13.15" thickBot="1">
+    <row r="15" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="149"/>
       <c r="B15" s="150"/>
       <c r="C15" s="150"/>
@@ -10272,9 +10280,9 @@
       <c r="E15" s="150"/>
       <c r="F15" s="150"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="159" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B16" s="160"/>
       <c r="C16" s="160"/>
@@ -10282,7 +10290,7 @@
       <c r="E16" s="160"/>
       <c r="F16" s="161"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="146"/>
       <c r="B17" s="147"/>
       <c r="C17" s="147"/>
@@ -10290,7 +10298,7 @@
       <c r="E17" s="147"/>
       <c r="F17" s="148"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="146"/>
       <c r="B18" s="147"/>
       <c r="C18" s="147"/>
@@ -10298,7 +10306,7 @@
       <c r="E18" s="147"/>
       <c r="F18" s="148"/>
     </row>
-    <row r="19" spans="1:6" ht="13.15" thickBot="1">
+    <row r="19" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="149"/>
       <c r="B19" s="150"/>
       <c r="C19" s="150"/>
@@ -10306,8 +10314,8 @@
       <c r="E19" s="150"/>
       <c r="F19" s="151"/>
     </row>
-    <row r="20" spans="1:6" ht="13.15" thickBot="1"/>
-    <row r="21" spans="1:6">
+    <row r="20" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="92" t="s">
         <v>3</v>
       </c>
@@ -10317,9 +10325,9 @@
       <c r="E21" s="152"/>
       <c r="F21" s="153"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="93" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B22" s="154"/>
       <c r="C22" s="154"/>
@@ -10327,9 +10335,9 @@
       <c r="E22" s="154"/>
       <c r="F22" s="155"/>
     </row>
-    <row r="23" spans="1:6" ht="13.15" thickBot="1">
+    <row r="23" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="94" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B23" s="156"/>
       <c r="C23" s="156"/>
@@ -10391,735 +10399,735 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="B2:J76"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="52"/>
+    <col min="1" max="1" width="8.69921875" style="52"/>
     <col min="2" max="2" width="25.5" style="52" customWidth="1"/>
-    <col min="3" max="3" width="8.75" style="52"/>
-    <col min="4" max="4" width="19.25" style="52" customWidth="1"/>
-    <col min="5" max="5" width="8.75" style="52"/>
-    <col min="6" max="6" width="21.75" style="52" customWidth="1"/>
-    <col min="7" max="16384" width="8.75" style="52"/>
+    <col min="3" max="3" width="8.69921875" style="52"/>
+    <col min="4" max="4" width="19.19921875" style="52" customWidth="1"/>
+    <col min="5" max="5" width="8.69921875" style="52"/>
+    <col min="6" max="6" width="21.69921875" style="52" customWidth="1"/>
+    <col min="7" max="16384" width="8.69921875" style="52"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="15" thickBot="1">
+    <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="66" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="53" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F2" s="52" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="J2" s="53" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="J2" s="53" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10">
-      <c r="B3" s="66" t="s">
+      <c r="D3" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="71" t="s">
+      <c r="F3" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" s="68" t="s">
         <v>107</v>
-      </c>
-      <c r="F3" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="H3" s="68" t="s">
-        <v>108</v>
       </c>
       <c r="I3" s="99"/>
       <c r="J3" s="56" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="66" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="F4" s="57" t="s">
         <v>110</v>
       </c>
-      <c r="F4" s="57" t="s">
+      <c r="H4" s="101" t="s">
         <v>111</v>
-      </c>
-      <c r="H4" s="101" t="s">
-        <v>112</v>
       </c>
       <c r="I4" s="68"/>
       <c r="J4" s="58" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="66" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="71" t="s">
+      <c r="F5" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="H5" s="68" t="s">
         <v>115</v>
       </c>
-      <c r="H5" s="68" t="s">
+      <c r="I5" s="100"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="I5" s="100"/>
-    </row>
-    <row r="6" spans="2:10">
-      <c r="B6" s="66" t="s">
+      <c r="D6" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="F6" s="57" t="s">
         <v>118</v>
       </c>
-      <c r="F6" s="57" t="s">
+      <c r="H6" s="99" t="s">
         <v>119</v>
       </c>
-      <c r="H6" s="99" t="s">
+      <c r="I6" s="101"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="I6" s="101"/>
-    </row>
-    <row r="7" spans="2:10">
-      <c r="B7" s="66" t="s">
+      <c r="D7" s="71" t="s">
         <v>121</v>
-      </c>
-      <c r="D7" s="71" t="s">
-        <v>122</v>
       </c>
       <c r="F7" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="I7" s="102"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="I7" s="102"/>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" s="66" t="s">
+      <c r="D8" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="F8" s="57" t="s">
         <v>125</v>
       </c>
-      <c r="F8" s="57" t="s">
+      <c r="H8" s="102" t="s">
         <v>126</v>
-      </c>
-      <c r="H8" s="102" t="s">
-        <v>127</v>
       </c>
       <c r="I8" s="99"/>
       <c r="J8" s="52" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="66" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="9" spans="2:10">
-      <c r="B9" s="66" t="s">
+      <c r="D9" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="F9" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="F9" s="59" t="s">
+      <c r="H9" s="103" t="s">
         <v>131</v>
-      </c>
-      <c r="H9" s="103" t="s">
-        <v>132</v>
       </c>
       <c r="I9" s="99"/>
       <c r="J9" s="52" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="66" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="54" t="s">
         <v>133</v>
       </c>
-      <c r="D10" s="54" t="s">
+      <c r="F10" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="F10" s="57" t="s">
+      <c r="H10" s="107" t="s">
         <v>135</v>
       </c>
-      <c r="H10" s="107" t="s">
+      <c r="I10" s="102"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="66" t="s">
         <v>136</v>
       </c>
-      <c r="I10" s="102"/>
-    </row>
-    <row r="11" spans="2:10">
-      <c r="B11" s="66" t="s">
+      <c r="D11" s="71" t="s">
         <v>137</v>
       </c>
-      <c r="D11" s="71" t="s">
+      <c r="F11" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="F11" s="59" t="s">
+      <c r="H11" s="103" t="s">
         <v>139</v>
-      </c>
-      <c r="H11" s="103" t="s">
-        <v>140</v>
       </c>
       <c r="I11" s="102"/>
       <c r="J11" s="52" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="66" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="12" spans="2:10">
-      <c r="B12" s="66" t="s">
+      <c r="F12" s="57" t="s">
         <v>142</v>
       </c>
-      <c r="F12" s="57" t="s">
+      <c r="H12" s="107" t="s">
         <v>143</v>
-      </c>
-      <c r="H12" s="107" t="s">
-        <v>144</v>
       </c>
       <c r="I12" s="103"/>
       <c r="J12" s="52" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="66" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="13" spans="2:10">
-      <c r="B13" s="66" t="s">
+      <c r="F13" s="59" t="s">
         <v>146</v>
       </c>
-      <c r="F13" s="59" t="s">
+      <c r="H13" s="104" t="s">
         <v>147</v>
       </c>
-      <c r="H13" s="104" t="s">
+      <c r="I13" s="103"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="66" t="s">
         <v>148</v>
-      </c>
-      <c r="I13" s="103"/>
-    </row>
-    <row r="14" spans="2:10">
-      <c r="B14" s="66" t="s">
-        <v>149</v>
       </c>
       <c r="D14" s="60"/>
       <c r="F14" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="H14" s="105" t="s">
         <v>150</v>
       </c>
-      <c r="H14" s="105" t="s">
+      <c r="I14" s="104"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="66" t="s">
         <v>151</v>
-      </c>
-      <c r="I14" s="104"/>
-    </row>
-    <row r="15" spans="2:10">
-      <c r="B15" s="66" t="s">
-        <v>152</v>
       </c>
       <c r="D15" s="61"/>
       <c r="F15" s="59" t="s">
+        <v>152</v>
+      </c>
+      <c r="H15" s="103" t="s">
         <v>153</v>
       </c>
-      <c r="H15" s="103" t="s">
+      <c r="I15" s="103"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="66" t="s">
         <v>154</v>
-      </c>
-      <c r="I15" s="103"/>
-    </row>
-    <row r="16" spans="2:10">
-      <c r="B16" s="66" t="s">
-        <v>155</v>
       </c>
       <c r="D16" s="61"/>
       <c r="F16" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="H16" s="104" t="s">
         <v>156</v>
       </c>
-      <c r="H16" s="104" t="s">
+      <c r="I16" s="105"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="66" t="s">
         <v>157</v>
-      </c>
-      <c r="I16" s="105"/>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" s="66" t="s">
-        <v>158</v>
       </c>
       <c r="D17" s="61"/>
       <c r="F17" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="H17" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="H17" s="67" t="s">
+      <c r="I17" s="103"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="66" t="s">
         <v>160</v>
-      </c>
-      <c r="I17" s="103"/>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="66" t="s">
-        <v>161</v>
       </c>
       <c r="D18" s="61"/>
       <c r="F18" s="57" t="s">
+        <v>161</v>
+      </c>
+      <c r="H18" s="108" t="s">
         <v>162</v>
       </c>
-      <c r="H18" s="108" t="s">
+      <c r="I18" s="105"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" s="66" t="s">
         <v>163</v>
-      </c>
-      <c r="I18" s="105"/>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" s="66" t="s">
-        <v>164</v>
       </c>
       <c r="D19" s="61"/>
       <c r="F19" s="59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H19" s="70" t="s">
+        <v>164</v>
+      </c>
+      <c r="I19" s="106"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B20" s="66" t="s">
         <v>165</v>
-      </c>
-      <c r="I19" s="106"/>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="66" t="s">
-        <v>166</v>
       </c>
       <c r="D20" s="61"/>
       <c r="F20" s="57" t="s">
+        <v>166</v>
+      </c>
+      <c r="H20" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="H20" s="70" t="s">
+      <c r="I20" s="104"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B21" s="66" t="s">
         <v>168</v>
-      </c>
-      <c r="I20" s="104"/>
-    </row>
-    <row r="21" spans="2:9">
-      <c r="B21" s="66" t="s">
-        <v>169</v>
       </c>
       <c r="D21" s="61"/>
       <c r="F21" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="H21" s="112" t="s">
         <v>170</v>
       </c>
-      <c r="H21" s="112" t="s">
+      <c r="I21" s="102"/>
+    </row>
+    <row r="22" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B22" s="66" t="s">
         <v>171</v>
-      </c>
-      <c r="I21" s="102"/>
-    </row>
-    <row r="22" spans="2:9" ht="27.6">
-      <c r="B22" s="66" t="s">
-        <v>172</v>
       </c>
       <c r="D22" s="61"/>
       <c r="F22" s="57" t="s">
+        <v>172</v>
+      </c>
+      <c r="H22" s="118" t="s">
         <v>173</v>
       </c>
-      <c r="H22" s="118" t="s">
+      <c r="I22" s="107"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B23" s="66" t="s">
         <v>174</v>
-      </c>
-      <c r="I22" s="107"/>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" s="66" t="s">
-        <v>175</v>
       </c>
       <c r="D23" s="61"/>
       <c r="F23" s="59" t="s">
+        <v>175</v>
+      </c>
+      <c r="H23" s="110" t="s">
+        <v>67</v>
+      </c>
+      <c r="I23" s="108"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B24" s="66" t="s">
         <v>176</v>
-      </c>
-      <c r="H23" s="110" t="s">
-        <v>68</v>
-      </c>
-      <c r="I23" s="108"/>
-    </row>
-    <row r="24" spans="2:9">
-      <c r="B24" s="66" t="s">
-        <v>177</v>
       </c>
       <c r="D24" s="61"/>
       <c r="F24" s="57" t="s">
+        <v>177</v>
+      </c>
+      <c r="H24" s="70" t="s">
         <v>178</v>
       </c>
-      <c r="H24" s="70" t="s">
+      <c r="I24" s="109"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B25" s="66" t="s">
         <v>179</v>
-      </c>
-      <c r="I24" s="109"/>
-    </row>
-    <row r="25" spans="2:9">
-      <c r="B25" s="66" t="s">
-        <v>180</v>
       </c>
       <c r="D25" s="61"/>
       <c r="F25" s="59" t="s">
+        <v>180</v>
+      </c>
+      <c r="H25" s="112" t="s">
         <v>181</v>
       </c>
-      <c r="H25" s="112" t="s">
+      <c r="I25" s="110"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B26" s="66" t="s">
         <v>182</v>
       </c>
-      <c r="I25" s="110"/>
-    </row>
-    <row r="26" spans="2:9">
-      <c r="B26" s="66" t="s">
+      <c r="F26" s="57" t="s">
         <v>183</v>
       </c>
-      <c r="F26" s="57" t="s">
+      <c r="H26" s="70" t="s">
         <v>184</v>
       </c>
-      <c r="H26" s="70" t="s">
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B27" s="66" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9">
-      <c r="B27" s="66" t="s">
-        <v>186</v>
       </c>
       <c r="D27" s="61"/>
       <c r="F27" s="59" t="s">
+        <v>186</v>
+      </c>
+      <c r="H27" s="109" t="s">
         <v>187</v>
       </c>
-      <c r="H27" s="109" t="s">
+      <c r="I27" s="108"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B28" s="66" t="s">
         <v>188</v>
-      </c>
-      <c r="I27" s="108"/>
-    </row>
-    <row r="28" spans="2:9">
-      <c r="B28" s="66" t="s">
-        <v>189</v>
       </c>
       <c r="D28" s="61"/>
       <c r="F28" s="57" t="s">
+        <v>189</v>
+      </c>
+      <c r="H28" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="H28" s="112" t="s">
+      <c r="I28" s="70"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B29" s="66" t="s">
         <v>191</v>
       </c>
-      <c r="I28" s="70"/>
-    </row>
-    <row r="29" spans="2:9">
-      <c r="B29" s="66" t="s">
+      <c r="F29" s="59" t="s">
         <v>192</v>
       </c>
-      <c r="F29" s="59" t="s">
+      <c r="H29" s="110" t="s">
         <v>193</v>
       </c>
-      <c r="H29" s="110" t="s">
+      <c r="I29" s="111"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B30" s="66" t="s">
         <v>194</v>
       </c>
-      <c r="I29" s="111"/>
-    </row>
-    <row r="30" spans="2:9">
-      <c r="B30" s="66" t="s">
+      <c r="F30" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="F30" s="57" t="s">
+      <c r="H30" s="69" t="s">
         <v>196</v>
       </c>
-      <c r="H30" s="69" t="s">
+      <c r="I30" s="109"/>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B31" s="66" t="s">
         <v>197</v>
       </c>
-      <c r="I30" s="109"/>
-    </row>
-    <row r="31" spans="2:9">
-      <c r="B31" s="66" t="s">
+      <c r="F31" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="F31" s="59" t="s">
+      <c r="H31" s="69" t="s">
         <v>199</v>
       </c>
-      <c r="H31" s="69" t="s">
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B32" s="66" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="32" spans="2:9">
-      <c r="B32" s="66" t="s">
+      <c r="F32" s="57" t="s">
         <v>201</v>
       </c>
-      <c r="F32" s="57" t="s">
+      <c r="H32" s="111" t="s">
         <v>202</v>
       </c>
-      <c r="H32" s="111" t="s">
+      <c r="I32" s="110"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B33" s="66" t="s">
         <v>203</v>
       </c>
-      <c r="I32" s="110"/>
-    </row>
-    <row r="33" spans="2:9">
-      <c r="B33" s="66" t="s">
+      <c r="F33" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="H33" s="119" t="s">
         <v>204</v>
       </c>
-      <c r="F33" s="59" t="s">
-        <v>99</v>
-      </c>
-      <c r="H33" s="119" t="s">
+      <c r="I33" s="110"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B34" s="66" t="s">
         <v>205</v>
       </c>
-      <c r="I33" s="110"/>
-    </row>
-    <row r="34" spans="2:9">
-      <c r="B34" s="66" t="s">
+      <c r="F34" s="57" t="s">
         <v>206</v>
-      </c>
-      <c r="F34" s="57" t="s">
-        <v>207</v>
       </c>
       <c r="H34" s="109" t="s">
         <v>1</v>
       </c>
       <c r="I34" s="69"/>
     </row>
-    <row r="35" spans="2:9">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35" s="66" t="s">
+        <v>207</v>
+      </c>
+      <c r="F35" s="59" t="s">
         <v>208</v>
       </c>
-      <c r="F35" s="59" t="s">
+      <c r="H35" s="114" t="s">
         <v>209</v>
       </c>
-      <c r="H35" s="114" t="s">
+      <c r="I35" s="109"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B36" s="66" t="s">
         <v>210</v>
       </c>
-      <c r="I35" s="109"/>
-    </row>
-    <row r="36" spans="2:9">
-      <c r="B36" s="66" t="s">
+      <c r="F36" s="57" t="s">
         <v>211</v>
       </c>
-      <c r="F36" s="57" t="s">
+      <c r="H36" s="111" t="s">
         <v>212</v>
       </c>
-      <c r="H36" s="111" t="s">
+      <c r="I36" s="102"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B37" s="66" t="s">
         <v>213</v>
       </c>
-      <c r="I36" s="102"/>
-    </row>
-    <row r="37" spans="2:9">
-      <c r="B37" s="66" t="s">
+      <c r="F37" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="F37" s="57" t="s">
+      <c r="H37" s="112" t="s">
         <v>215</v>
       </c>
-      <c r="H37" s="112" t="s">
+      <c r="I37" s="110"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B38" s="66" t="s">
         <v>216</v>
-      </c>
-      <c r="I37" s="110"/>
-    </row>
-    <row r="38" spans="2:9">
-      <c r="B38" s="66" t="s">
-        <v>217</v>
       </c>
       <c r="F38" s="57" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="109" t="s">
+        <v>217</v>
+      </c>
+      <c r="I38" s="109"/>
+    </row>
+    <row r="39" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B39" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="I38" s="109"/>
-    </row>
-    <row r="39" spans="2:9" ht="27.6">
-      <c r="B39" s="66" t="s">
+      <c r="F39" s="57" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="57" t="s">
+      <c r="H39" s="109" t="s">
         <v>220</v>
       </c>
-      <c r="H39" s="109" t="s">
+      <c r="I39" s="111"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B40" s="66" t="s">
         <v>221</v>
       </c>
-      <c r="I39" s="111"/>
-    </row>
-    <row r="40" spans="2:9">
-      <c r="B40" s="66" t="s">
+      <c r="F40" s="59" t="s">
         <v>222</v>
       </c>
-      <c r="F40" s="59" t="s">
+      <c r="H40" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="H40" s="69" t="s">
+      <c r="I40" s="112"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B41" s="66" t="s">
         <v>224</v>
-      </c>
-      <c r="I40" s="112"/>
-    </row>
-    <row r="41" spans="2:9">
-      <c r="B41" s="66" t="s">
-        <v>225</v>
       </c>
       <c r="D41" s="63"/>
       <c r="H41" s="111" t="s">
+        <v>225</v>
+      </c>
+      <c r="I41" s="112"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B42" s="66" t="s">
         <v>226</v>
       </c>
-      <c r="I41" s="112"/>
-    </row>
-    <row r="42" spans="2:9">
-      <c r="B42" s="66" t="s">
+      <c r="H42" s="112" t="s">
         <v>227</v>
       </c>
-      <c r="H42" s="112" t="s">
+      <c r="I42" s="109"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B43" s="66" t="s">
         <v>228</v>
       </c>
-      <c r="I42" s="109"/>
-    </row>
-    <row r="43" spans="2:9">
-      <c r="B43" s="66" t="s">
+      <c r="H43" s="109" t="s">
         <v>229</v>
       </c>
-      <c r="H43" s="109" t="s">
+      <c r="I43" s="111"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B44" s="121" t="s">
         <v>230</v>
       </c>
-      <c r="I43" s="111"/>
-    </row>
-    <row r="44" spans="2:9">
-      <c r="B44" s="121" t="s">
+      <c r="H44" s="111" t="s">
         <v>231</v>
       </c>
-      <c r="H44" s="111" t="s">
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H45" s="112" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="45" spans="2:9">
-      <c r="H45" s="112" t="s">
+      <c r="I45" s="110"/>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H46" s="70" t="s">
         <v>233</v>
       </c>
-      <c r="I45" s="110"/>
-    </row>
-    <row r="46" spans="2:9">
-      <c r="H46" s="70" t="s">
-        <v>234</v>
-      </c>
       <c r="I46" s="113"/>
     </row>
-    <row r="47" spans="2:9">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47" s="62"/>
       <c r="H47" s="112" t="s">
+        <v>234</v>
+      </c>
+      <c r="I47" s="112"/>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H48" s="70" t="s">
         <v>235</v>
       </c>
-      <c r="I47" s="112"/>
-    </row>
-    <row r="48" spans="2:9">
-      <c r="H48" s="70" t="s">
+      <c r="I48" s="112"/>
+    </row>
+    <row r="49" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H49" s="109" t="s">
         <v>236</v>
       </c>
-      <c r="I48" s="112"/>
-    </row>
-    <row r="49" spans="8:9">
-      <c r="H49" s="109" t="s">
+      <c r="I49" s="112"/>
+    </row>
+    <row r="50" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H50" s="70" t="s">
         <v>237</v>
       </c>
-      <c r="I49" s="112"/>
-    </row>
-    <row r="50" spans="8:9">
-      <c r="H50" s="70" t="s">
+      <c r="I50" s="112"/>
+    </row>
+    <row r="51" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H51" s="69" t="s">
         <v>238</v>
       </c>
-      <c r="I50" s="112"/>
-    </row>
-    <row r="51" spans="8:9">
-      <c r="H51" s="69" t="s">
+      <c r="I51" s="112"/>
+    </row>
+    <row r="52" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H52" s="112" t="s">
         <v>239</v>
       </c>
-      <c r="I51" s="112"/>
-    </row>
-    <row r="52" spans="8:9">
-      <c r="H52" s="112" t="s">
+    </row>
+    <row r="53" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H53" s="109" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="53" spans="8:9">
-      <c r="H53" s="109" t="s">
+      <c r="I53" s="112"/>
+    </row>
+    <row r="54" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H54" s="69" t="s">
         <v>241</v>
       </c>
-      <c r="I53" s="112"/>
-    </row>
-    <row r="54" spans="8:9">
-      <c r="H54" s="69" t="s">
+      <c r="I54" s="111"/>
+    </row>
+    <row r="55" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H55" s="70" t="s">
         <v>242</v>
       </c>
-      <c r="I54" s="111"/>
-    </row>
-    <row r="55" spans="8:9">
-      <c r="H55" s="70" t="s">
+      <c r="I55" s="111"/>
+    </row>
+    <row r="56" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H56" s="109" t="s">
         <v>243</v>
       </c>
-      <c r="I55" s="111"/>
-    </row>
-    <row r="56" spans="8:9">
-      <c r="H56" s="109" t="s">
+      <c r="I56" s="70"/>
+    </row>
+    <row r="57" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H57" s="70" t="s">
         <v>244</v>
       </c>
-      <c r="I56" s="70"/>
-    </row>
-    <row r="57" spans="8:9">
-      <c r="H57" s="70" t="s">
+      <c r="I57" s="112"/>
+    </row>
+    <row r="58" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H58" s="70" t="s">
         <v>245</v>
       </c>
-      <c r="I57" s="112"/>
-    </row>
-    <row r="58" spans="8:9">
-      <c r="H58" s="70" t="s">
+      <c r="I58" s="112"/>
+    </row>
+    <row r="59" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H59" s="112" t="s">
         <v>246</v>
       </c>
-      <c r="I58" s="112"/>
-    </row>
-    <row r="59" spans="8:9">
-      <c r="H59" s="112" t="s">
+      <c r="I59" s="115"/>
+    </row>
+    <row r="60" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H60" s="115" t="s">
         <v>247</v>
       </c>
-      <c r="I59" s="115"/>
-    </row>
-    <row r="60" spans="8:9">
-      <c r="H60" s="115" t="s">
+      <c r="I60" s="69"/>
+    </row>
+    <row r="61" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H61" s="69" t="s">
         <v>248</v>
       </c>
-      <c r="I60" s="69"/>
-    </row>
-    <row r="61" spans="8:9">
-      <c r="H61" s="69" t="s">
+      <c r="I61" s="110"/>
+    </row>
+    <row r="62" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H62" s="69" t="s">
         <v>249</v>
       </c>
-      <c r="I61" s="110"/>
-    </row>
-    <row r="62" spans="8:9">
-      <c r="H62" s="69" t="s">
+      <c r="I62" s="69"/>
+    </row>
+    <row r="63" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H63" s="110" t="s">
         <v>250</v>
       </c>
-      <c r="I62" s="69"/>
-    </row>
-    <row r="63" spans="8:9">
-      <c r="H63" s="110" t="s">
+    </row>
+    <row r="64" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H64" s="120" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="64" spans="8:9">
-      <c r="H64" s="120" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="65" spans="8:8">
+    <row r="65" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H65" s="111"/>
     </row>
-    <row r="66" spans="8:8">
+    <row r="66" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H66" s="109"/>
     </row>
-    <row r="67" spans="8:8">
+    <row r="67" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H67" s="112"/>
     </row>
-    <row r="68" spans="8:8">
+    <row r="68" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H68" s="102"/>
     </row>
-    <row r="69" spans="8:8">
+    <row r="69" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H69" s="112"/>
     </row>
-    <row r="70" spans="8:8">
+    <row r="70" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H70" s="70"/>
     </row>
-    <row r="71" spans="8:8">
+    <row r="71" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H71" s="109"/>
     </row>
-    <row r="72" spans="8:8">
+    <row r="72" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H72" s="111"/>
     </row>
-    <row r="73" spans="8:8">
+    <row r="73" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H73" s="100"/>
     </row>
-    <row r="74" spans="8:8">
+    <row r="74" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H74" s="107"/>
     </row>
-    <row r="75" spans="8:8">
+    <row r="75" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H75" s="116"/>
     </row>
-    <row r="76" spans="8:8">
+    <row r="76" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H76" s="116"/>
     </row>
   </sheetData>
@@ -11138,21 +11146,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -11290,16 +11283,54 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A69B405-5052-432A-9FF7-5BE9AD104741}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BCE9238-FF1F-4C61-A5D2-EFCC7F17A0B5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8BD9242-4DDC-4F33-9117-AF226C9C4E38}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8BD9242-4DDC-4F33-9117-AF226C9C4E38}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BCE9238-FF1F-4C61-A5D2-EFCC7F17A0B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A69B405-5052-432A-9FF7-5BE9AD104741}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
